--- a/docs/Files/Mid-format_model/ODYM_Config_Tutorial6_MF_model_1.xlsx
+++ b/docs/Files/Mid-format_model/ODYM_Config_Tutorial6_MF_model_1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elanphear\Code\ODYM\docs\Files\Mid-format_model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20A2C074-6E7F-497A-8E94-240E23202F9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{209CAA9B-69C4-4C68-BF1A-7B21455A90F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="844" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -357,9 +357,6 @@
     <t>10_World_Regions</t>
   </si>
   <si>
-    <t>[310:324)</t>
-  </si>
-  <si>
     <t>Battery lifetime</t>
   </si>
   <si>
@@ -517,6 +514,9 @@
   </si>
   <si>
     <t>Distribution of after recycling going to other (non MF LIB) production. Based on ODYM_Tutorial6_SectorSplitLL</t>
+  </si>
+  <si>
+    <t>[313:324)</t>
   </si>
 </sst>
 </file>
@@ -1329,7 +1329,7 @@
         <v>4</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.35">
@@ -1337,7 +1337,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.35">
@@ -1384,7 +1384,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J10" s="13"/>
     </row>
@@ -1462,7 +1462,7 @@
         <v>11</v>
       </c>
       <c r="G16" t="s">
-        <v>107</v>
+        <v>160</v>
       </c>
       <c r="H16" s="21" t="s">
         <v>23</v>
@@ -1485,7 +1485,7 @@
         <v>11</v>
       </c>
       <c r="G17" t="s">
-        <v>107</v>
+        <v>160</v>
       </c>
       <c r="H17" s="21" t="s">
         <v>75</v>
@@ -1508,7 +1508,7 @@
         <v>22</v>
       </c>
       <c r="G18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H18" s="21" t="s">
         <v>24</v>
@@ -1693,7 +1693,7 @@
         <v>84</v>
       </c>
       <c r="F28" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.35">
@@ -1707,7 +1707,7 @@
         <v>54</v>
       </c>
       <c r="F29" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.35">
@@ -1715,13 +1715,13 @@
         <v>2</v>
       </c>
       <c r="D30" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E30" t="s">
         <v>54</v>
       </c>
       <c r="F30" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.35">
@@ -1729,13 +1729,13 @@
         <v>3</v>
       </c>
       <c r="D31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E31" t="s">
         <v>54</v>
       </c>
       <c r="F31" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.35">
@@ -1743,13 +1743,13 @@
         <v>4</v>
       </c>
       <c r="D32" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E32" t="s">
         <v>55</v>
       </c>
       <c r="F32" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.35">
@@ -1757,13 +1757,13 @@
         <v>5</v>
       </c>
       <c r="D33" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E33" t="s">
         <v>54</v>
       </c>
       <c r="F33" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.35">
@@ -1771,13 +1771,13 @@
         <v>6</v>
       </c>
       <c r="D34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E34" t="s">
         <v>54</v>
       </c>
       <c r="F34" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.35">
@@ -1785,13 +1785,13 @@
         <v>7</v>
       </c>
       <c r="D35" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E35" t="s">
         <v>54</v>
       </c>
       <c r="F35" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.35">
@@ -1799,13 +1799,13 @@
         <v>8</v>
       </c>
       <c r="D36" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E36" t="s">
         <v>55</v>
       </c>
       <c r="F36" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.35">
@@ -1844,10 +1844,10 @@
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C40" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D40" s="38" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E40" t="s">
         <v>94</v>
@@ -1867,10 +1867,10 @@
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C41" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="D41" t="s">
         <v>158</v>
-      </c>
-      <c r="D41" t="s">
-        <v>159</v>
       </c>
       <c r="E41" t="s">
         <v>94</v>
@@ -1890,10 +1890,10 @@
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C42" s="27" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D42" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E42" t="s">
         <v>94</v>
@@ -1908,15 +1908,15 @@
         <v>31</v>
       </c>
       <c r="I42" s="41" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C43" s="27" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D43" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E43" t="s">
         <v>94</v>
@@ -1931,15 +1931,15 @@
         <v>31</v>
       </c>
       <c r="I43" s="41" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C44" s="27" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D44" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E44" t="s">
         <v>94</v>
@@ -1954,15 +1954,15 @@
         <v>31</v>
       </c>
       <c r="I44" s="41" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C45" s="27" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D45" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E45" t="s">
         <v>94</v>
@@ -1977,15 +1977,15 @@
         <v>31</v>
       </c>
       <c r="I45" s="43" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C46" s="27" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D46" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E46" t="s">
         <v>94</v>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C47" s="44" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D47" s="45" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E47" s="45" t="s">
         <v>94</v>
@@ -2023,15 +2023,15 @@
         <v>31</v>
       </c>
       <c r="I47" s="46" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C48" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D48" s="45" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E48" s="45" t="s">
         <v>94</v>
@@ -2046,15 +2046,15 @@
         <v>31</v>
       </c>
       <c r="I48" s="46" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C49" s="44" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D49" s="45" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E49" s="45" t="s">
         <v>94</v>
@@ -2069,15 +2069,15 @@
         <v>31</v>
       </c>
       <c r="I49" s="46" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C50" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="D50" s="45" t="s">
         <v>142</v>
-      </c>
-      <c r="D50" s="45" t="s">
-        <v>143</v>
       </c>
       <c r="E50" s="45" t="s">
         <v>94</v>
@@ -2092,15 +2092,15 @@
         <v>31</v>
       </c>
       <c r="I50" s="46" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C51" s="44" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D51" s="45" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E51" s="45" t="s">
         <v>94</v>
@@ -2115,12 +2115,12 @@
         <v>31</v>
       </c>
       <c r="I51" s="46" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C52" s="27" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D52" t="s">
         <v>101</v>
